--- a/artfynd/A 61493-2025 artfynd.xlsx
+++ b/artfynd/A 61493-2025 artfynd.xlsx
@@ -675,48 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3000042</v>
+        <v>88404965</v>
       </c>
       <c r="B2" t="n">
-        <v>98646</v>
+        <v>92567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>barrskog 500 m OSO om KARLSHED, Vg</t>
+          <t>Mark Karlshed, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>362981</v>
+        <v>362946</v>
       </c>
       <c r="R2" t="n">
-        <v>6373922</v>
+        <v>6373951</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>44</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1998-07-10</t>
+          <t>2020-09-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1998-07-10</t>
+          <t>2020-09-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,37 +771,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Mathias Bergeld</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kenneth Hansson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Västergötlands flora 2002</t>
-        </is>
-      </c>
+          <t>Mathias Bergeld</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3051425</v>
+        <v>3000042</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,34 +818,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Karlshedskogen, Vg</t>
+          <t>barrskog 500 m OSO om KARLSHED, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362858.3809951592</v>
+        <v>362981</v>
       </c>
       <c r="R3" t="n">
-        <v>6373755.917108714</v>
+        <v>6373922</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,22 +855,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-08-20</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-08-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1998-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,80 +872,81 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>torr barrskog</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Kenneth Hansson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Kenneth Hansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88404965</v>
+        <v>3051425</v>
       </c>
       <c r="B4" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mark Karlshed, Vg</t>
+          <t>Karlshedskogen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>362946.35469807</v>
+        <v>362858</v>
       </c>
       <c r="R4" t="n">
-        <v>6373951.457358168</v>
+        <v>6373756</v>
       </c>
       <c r="S4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,22 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2011-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2011-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,19 +984,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>torr barrskog</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mathias Bergeld</t>
+          <t>Kenneth Hansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mathias Bergeld</t>
+          <t>Kenneth Hansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1030,12 +1010,7 @@
         <v>17212482</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>363007.7284979688</v>
+        <v>363008</v>
       </c>
       <c r="R5" t="n">
-        <v>6373805.222432519</v>
+        <v>6373805</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1120,19 +1095,9 @@
           <t>2014-08-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-08-17</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
